--- a/结果/问题二_增强优化版.xlsx
+++ b/结果/问题二_增强优化版.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N46"/>
+  <dimension ref="A1:N45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -671,17 +671,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>UA01</t>
+          <t>UB01</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>A-BAT-01</t>
+          <t>B-BAT-01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -691,17 +691,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>S006-WAT-01,S006-MED-01</t>
+          <t>S006-WAT-01,S006-WAT-02</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>15.56128209955562</v>
+        <v>14.67766295665795</v>
       </c>
       <c r="I5" t="n">
-        <v>21.83045308800013</v>
+        <v>20.06321480220478</v>
       </c>
       <c r="J5" t="n">
         <v>60</v>
@@ -710,13 +710,13 @@
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>1.106805665390136</v>
+        <v>1.087081446911481</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7540431854688587</v>
+        <v>0.7282296382721298</v>
       </c>
       <c r="N5" t="n">
-        <v>13.66239764817473</v>
+        <v>18.96225489436069</v>
       </c>
     </row>
     <row r="6">
@@ -725,7 +725,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>UB01</t>
+          <t>UB02</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -735,27 +735,27 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>B-BAT-01</t>
+          <t>B-BAT-02</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>S007</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>S007-WAT-01,S007-WAT-02</t>
+          <t>S006-WAT-03,S006-MED-01</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>17.67022540924516</v>
+        <v>14.67766295665795</v>
       </c>
       <c r="I6" t="n">
-        <v>26.08578415182364</v>
+        <v>20.06321480220478</v>
       </c>
       <c r="J6" t="n">
         <v>60</v>
@@ -764,13 +764,13 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>1.60089897336792</v>
+        <v>0.9613264853346692</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5997752566580201</v>
+        <v>0.7596683786663327</v>
       </c>
       <c r="N6" t="n">
-        <v>22.67315925210164</v>
+        <v>18.05402461630594</v>
       </c>
     </row>
     <row r="7">
@@ -779,37 +779,37 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>UB02</t>
+          <t>UA01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>B-BAT-02</t>
+          <t>A-BAT-01</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>S010</t>
+          <t>S007</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>S010-WAT-01,S010-MED-01</t>
+          <t>S007-WAT-01,S007-MED-01</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>17.01750341526321</v>
+        <v>18.92962030802469</v>
       </c>
       <c r="I7" t="n">
-        <v>24.7837846083042</v>
+        <v>28.60457394938271</v>
       </c>
       <c r="J7" t="n">
         <v>60</v>
@@ -818,13 +818,13 @@
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>1.424415898434041</v>
+        <v>1.629423413491632</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6438960253914898</v>
+        <v>0.6379059081129708</v>
       </c>
       <c r="N7" t="n">
-        <v>21.39855926646807</v>
+        <v>16.17870532421897</v>
       </c>
     </row>
     <row r="8">
@@ -848,22 +848,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>S013</t>
+          <t>S010</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>S013-WAT-01,S013-MED-01</t>
+          <t>S010-WAT-01,S010-MED-01</t>
         </is>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>18.04073685958943</v>
+        <v>18.34484599897648</v>
       </c>
       <c r="I8" t="n">
-        <v>26.83036260806776</v>
+        <v>27.43846977573074</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
@@ -872,13 +872,13 @@
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>1.637365079674389</v>
+        <v>1.642792520169815</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6361410934056912</v>
+        <v>0.6349349955178188</v>
       </c>
       <c r="N8" t="n">
-        <v>16.21694297621002</v>
+        <v>16.24307509711392</v>
       </c>
     </row>
     <row r="9">
@@ -887,37 +887,37 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>UA03</t>
+          <t>UB01</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>A-BAT-03</t>
+          <t>B-BAT-03</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>S012</t>
+          <t>S013</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>S012-WAT-01,S012-MED-01</t>
+          <t>S013-WAT-01,S013-MED-01</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>20.06321480220478</v>
       </c>
       <c r="H9" t="n">
-        <v>22.2385339731365</v>
+        <v>36.75709046662761</v>
       </c>
       <c r="I9" t="n">
-        <v>35.146067946273</v>
+        <v>44.19985501993932</v>
       </c>
       <c r="J9" t="n">
         <v>60</v>
@@ -926,13 +926,13 @@
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>2.471325003399136</v>
+        <v>1.416012022961981</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4508166659113031</v>
+        <v>0.6459969942595047</v>
       </c>
       <c r="N9" t="n">
-        <v>20.23230557192176</v>
+        <v>21.33786461028097</v>
       </c>
     </row>
     <row r="10">
@@ -941,7 +941,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>UA04</t>
+          <t>UA03</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -951,27 +951,27 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>A-BAT-04</t>
+          <t>A-BAT-03</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>S014</t>
+          <t>S012</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>S014-WAT-01,S014-MED-01</t>
+          <t>S012-WAT-01,S012-MED-01</t>
         </is>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>21.21667202957535</v>
+        <v>22.2385339731365</v>
       </c>
       <c r="I10" t="n">
-        <v>33.18145517026183</v>
+        <v>35.146067946273</v>
       </c>
       <c r="J10" t="n">
         <v>60</v>
@@ -980,13 +980,13 @@
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>1.974536954059142</v>
+        <v>2.471325003399136</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5612140102090795</v>
+        <v>0.4508166659113031</v>
       </c>
       <c r="N10" t="n">
-        <v>17.84036311213661</v>
+        <v>20.23230557192176</v>
       </c>
     </row>
     <row r="11">
@@ -995,7 +995,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UA01</t>
+          <t>UA04</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1005,27 +1005,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>A-BAT-05</t>
+          <t>A-BAT-04</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S014</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>S006-WAT-02</t>
+          <t>S014-WAT-01,S014-MED-01</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>21.83045308800013</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>36.39173518755575</v>
+        <v>21.21667202957535</v>
       </c>
       <c r="I11" t="n">
-        <v>42.66090617600025</v>
+        <v>33.18145517026183</v>
       </c>
       <c r="J11" t="n">
         <v>60</v>
@@ -1034,13 +1034,13 @@
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>1.092476706316119</v>
+        <v>1.974536954059142</v>
       </c>
       <c r="M11" t="n">
-        <v>0.757227398596418</v>
+        <v>0.5612140102090795</v>
       </c>
       <c r="N11" t="n">
-        <v>13.59340636374428</v>
+        <v>17.84036311213661</v>
       </c>
     </row>
     <row r="12">
@@ -1059,27 +1059,27 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>A-BAT-06</t>
+          <t>A-BAT-05</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S007</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>S006-WAT-03</t>
+          <t>S007-WAT-02</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>26.83036260806776</v>
+        <v>27.43846977573074</v>
       </c>
       <c r="H12" t="n">
-        <v>41.39164470762339</v>
+        <v>45.36809008375543</v>
       </c>
       <c r="I12" t="n">
-        <v>47.66081569606789</v>
+        <v>55.04304372511346</v>
       </c>
       <c r="J12" t="n">
         <v>60</v>
@@ -1088,13 +1088,13 @@
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>1.092476706316119</v>
+        <v>1.609000793511423</v>
       </c>
       <c r="M12" t="n">
-        <v>0.757227398596418</v>
+        <v>0.6424442681085727</v>
       </c>
       <c r="N12" t="n">
-        <v>13.59340636374428</v>
+        <v>16.08037419098092</v>
       </c>
     </row>
     <row r="13">
@@ -1103,52 +1103,52 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>UB02</t>
+          <t>UC02</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>B-BAT-03</t>
+          <t>C-BAT-04</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>S007</t>
+          <t>S003</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>S007-MED-01</t>
+          <t>S003-WAT-01,S003-WAT-02,S003-WAT-03,S003-WAT-04,S003-MED-01</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>24.7837846083042</v>
+        <v>34.05455664662419</v>
       </c>
       <c r="H13" t="n">
-        <v>41.45401001754935</v>
+        <v>60.30281060642601</v>
       </c>
       <c r="I13" t="n">
-        <v>49.86956876012783</v>
+        <v>73.40239789956115</v>
       </c>
       <c r="J13" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="K13" t="b">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>1.278665737006417</v>
+        <v>5.440500810633867</v>
       </c>
       <c r="M13" t="n">
-        <v>0.6803335657483958</v>
+        <v>0.3199373986707666</v>
       </c>
       <c r="N13" t="n">
-        <v>20.34591921171301</v>
+        <v>38.44670504800009</v>
       </c>
     </row>
     <row r="14">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>UC02</t>
+          <t>UC01</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1167,27 +1167,27 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C-BAT-04</t>
+          <t>C-BAT-01</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>S003-WAT-01,S003-WAT-02,S003-WAT-03,S003-WAT-04,S003-MED-01</t>
+          <t>S008-WAT-01,S008-WAT-02,S008-MED-01</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>34.05455664662419</v>
+        <v>51.62987554632827</v>
       </c>
       <c r="H14" t="n">
-        <v>60.30281060642601</v>
+        <v>74.37264188394303</v>
       </c>
       <c r="I14" t="n">
-        <v>73.40239789956115</v>
+        <v>86.05407488822445</v>
       </c>
       <c r="J14" t="n">
         <v>120</v>
@@ -1196,13 +1196,13 @@
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>5.440500810633867</v>
+        <v>4.880456740806956</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3199373986707666</v>
+        <v>0.3899429073991305</v>
       </c>
       <c r="N14" t="n">
-        <v>38.44670504800009</v>
+        <v>35.91872834392029</v>
       </c>
     </row>
     <row r="15">
@@ -1211,37 +1211,37 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>UC01</t>
+          <t>UB02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>C-BAT-01</t>
+          <t>B-BAT-04</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S004</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>S008-WAT-01,S008-WAT-02,S008-MED-01</t>
+          <t>S004-WAT-01,S004-WAT-02</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>51.62987554632827</v>
+        <v>20.06321480220478</v>
       </c>
       <c r="H15" t="n">
-        <v>74.37264188394303</v>
+        <v>40.88082142764576</v>
       </c>
       <c r="I15" t="n">
-        <v>86.05407488822445</v>
+        <v>52.3102058308645</v>
       </c>
       <c r="J15" t="n">
         <v>120</v>
@@ -1250,13 +1250,13 @@
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>4.880456740806956</v>
+        <v>2.546881484042609</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3899429073991305</v>
+        <v>0.3632796289893477</v>
       </c>
       <c r="N15" t="n">
-        <v>35.91872834392029</v>
+        <v>29.50525516252995</v>
       </c>
     </row>
     <row r="16">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>B-BAT-04</t>
+          <t>B-BAT-02</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1285,17 +1285,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>S004-WAT-01,S004-WAT-02</t>
+          <t>S004-WAT-03,S004-MED-01</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>26.08578415182364</v>
+        <v>44.19985501993932</v>
       </c>
       <c r="H16" t="n">
-        <v>46.90339077726461</v>
+        <v>65.01746164538029</v>
       </c>
       <c r="I16" t="n">
-        <v>58.33277518048336</v>
+        <v>76.44684604859904</v>
       </c>
       <c r="J16" t="n">
         <v>120</v>
@@ -1304,13 +1304,13 @@
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>2.546881484042609</v>
+        <v>2.240674227365981</v>
       </c>
       <c r="M16" t="n">
-        <v>0.3632796289893477</v>
+        <v>0.4398314431585046</v>
       </c>
       <c r="N16" t="n">
-        <v>29.50525516252995</v>
+        <v>27.29375830875431</v>
       </c>
     </row>
     <row r="17">
@@ -1319,37 +1319,37 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>UB02</t>
+          <t>UA01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B-BAT-02</t>
+          <t>A-BAT-06</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>S004</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>S004-WAT-03,S004-MED-01</t>
+          <t>S001-FOD-01,S001-FOD-02</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>49.86956876012783</v>
+        <v>28.60457394938271</v>
       </c>
       <c r="H17" t="n">
-        <v>70.68717538556881</v>
+        <v>43.82841392100908</v>
       </c>
       <c r="I17" t="n">
-        <v>82.11655978878755</v>
+        <v>49.61480944819101</v>
       </c>
       <c r="J17" t="n">
         <v>120</v>
@@ -1358,13 +1358,13 @@
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>2.240674227365981</v>
+        <v>1.048835444247772</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4398314431585046</v>
+        <v>0.7669254568338284</v>
       </c>
       <c r="N17" t="n">
-        <v>27.29375830875431</v>
+        <v>13.38328176860038</v>
       </c>
     </row>
     <row r="18">
@@ -1383,27 +1383,27 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>A-BAT-01</t>
+          <t>A-BAT-02</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>S001-FOD-01,S001-FOD-02</t>
+          <t>S002-FOD-01,S002-FOD-02</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>35.49285073617485</v>
+        <v>43.68154487284467</v>
       </c>
       <c r="H18" t="n">
-        <v>50.71669070780122</v>
+        <v>65.09986638392333</v>
       </c>
       <c r="I18" t="n">
-        <v>56.50308623498314</v>
+        <v>77.12018789500198</v>
       </c>
       <c r="J18" t="n">
         <v>120</v>
@@ -1412,13 +1412,13 @@
         <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>1.048835444247772</v>
+        <v>2.409990591769786</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7669254568338284</v>
+        <v>0.4644465351622699</v>
       </c>
       <c r="N18" t="n">
-        <v>13.38328176860038</v>
+        <v>19.93699173815082</v>
       </c>
     </row>
     <row r="19">
@@ -1427,37 +1427,37 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>UA03</t>
+          <t>UB02</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>A-BAT-02</t>
+          <t>B-BAT-01</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S015</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>S002-FOD-01,S002-FOD-02</t>
+          <t>S015-MED-01</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>43.04730558427778</v>
+        <v>52.3102058308645</v>
       </c>
       <c r="H19" t="n">
-        <v>64.46562709535644</v>
+        <v>70.57757402331404</v>
       </c>
       <c r="I19" t="n">
-        <v>76.48594860643509</v>
+        <v>80.73027554909692</v>
       </c>
       <c r="J19" t="n">
         <v>120</v>
@@ -1466,13 +1466,13 @@
         <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>2.409990591769786</v>
+        <v>1.626892710624575</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4644465351622699</v>
+        <v>0.5932768223438563</v>
       </c>
       <c r="N19" t="n">
-        <v>19.93699173815082</v>
+        <v>22.86089179895526</v>
       </c>
     </row>
     <row r="20">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>UA01</t>
+          <t>UA03</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1491,27 +1491,27 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>A-BAT-04</t>
+          <t>A-BAT-01</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>S015</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>S015-MED-01</t>
+          <t>S001-FOD-03</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>51.02181828239844</v>
+        <v>44.78327927360168</v>
       </c>
       <c r="H20" t="n">
-        <v>70.96116026223557</v>
+        <v>59.00711924522805</v>
       </c>
       <c r="I20" t="n">
-        <v>82.78583557540601</v>
+        <v>64.79351477240996</v>
       </c>
       <c r="J20" t="n">
         <v>120</v>
@@ -1520,13 +1520,13 @@
         <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>1.976874086653691</v>
+        <v>1.014245103020607</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5606946474102907</v>
+        <v>0.7746121993287539</v>
       </c>
       <c r="N20" t="n">
-        <v>17.85161597277703</v>
+        <v>13.21673568121033</v>
       </c>
     </row>
     <row r="21">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>UA02</t>
+          <t>UA01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1545,27 +1545,27 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>A-BAT-03</t>
+          <t>A-BAT-04</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>S001-FOD-03</t>
+          <t>S006-FOD-01</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>55.37837351819476</v>
+        <v>51.02181828239844</v>
       </c>
       <c r="H21" t="n">
-        <v>69.60221348982112</v>
+        <v>65.58310038195407</v>
       </c>
       <c r="I21" t="n">
-        <v>75.38860901700306</v>
+        <v>71.85227137039857</v>
       </c>
       <c r="J21" t="n">
         <v>120</v>
@@ -1574,13 +1574,13 @@
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>1.014245103020607</v>
+        <v>1.066023243410243</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7746121993287539</v>
+        <v>0.7631059459088348</v>
       </c>
       <c r="N21" t="n">
-        <v>13.21673568121033</v>
+        <v>13.46603783864191</v>
       </c>
     </row>
     <row r="22">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>UA04</t>
+          <t>UA02</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1599,27 +1599,27 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>A-BAT-05</t>
+          <t>A-BAT-03</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S007</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>S006-FOD-01</t>
+          <t>S007-FOD-01</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>56.50308623498314</v>
+        <v>55.37837351819476</v>
       </c>
       <c r="H22" t="n">
-        <v>71.06436833453876</v>
+        <v>73.30799382621946</v>
       </c>
       <c r="I22" t="n">
-        <v>77.33353932298327</v>
+        <v>82.98294746757747</v>
       </c>
       <c r="J22" t="n">
         <v>120</v>
@@ -1628,13 +1628,13 @@
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>1.066023243410243</v>
+        <v>1.571297495086422</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7631059459088348</v>
+        <v>0.6508227788696839</v>
       </c>
       <c r="N22" t="n">
-        <v>13.46603783864191</v>
+        <v>15.89883979115685</v>
       </c>
     </row>
     <row r="23">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>UA02</t>
+          <t>UA03</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1658,22 +1658,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>S007</t>
+          <t>S010</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>S007-FOD-01</t>
+          <t>S010-FOD-01</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>75.38860901700306</v>
+        <v>64.79351477240996</v>
       </c>
       <c r="H23" t="n">
-        <v>93.31822932502776</v>
+        <v>82.13836077138644</v>
       </c>
       <c r="I23" t="n">
-        <v>102.9931829663858</v>
+        <v>91.2319845481407</v>
       </c>
       <c r="J23" t="n">
         <v>120</v>
@@ -1682,13 +1682,13 @@
         <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>1.571297495086422</v>
+        <v>1.581530554767664</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6508227788696839</v>
+        <v>0.6485487656071858</v>
       </c>
       <c r="N23" t="n">
-        <v>15.89883979115685</v>
+        <v>15.94811007851097</v>
       </c>
     </row>
     <row r="24">
@@ -1697,37 +1697,37 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>UA03</t>
+          <t>UB01</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>A-BAT-01</t>
+          <t>B-BAT-03</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>S010</t>
+          <t>S012</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>S010-FOD-01</t>
+          <t>S012-FOD-01</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>76.48594860643509</v>
+        <v>76.44684604859904</v>
       </c>
       <c r="H24" t="n">
-        <v>93.83079460541157</v>
+        <v>95.6302579822556</v>
       </c>
       <c r="I24" t="n">
-        <v>102.9244183821658</v>
+        <v>106.4826699159122</v>
       </c>
       <c r="J24" t="n">
         <v>120</v>
@@ -1736,13 +1736,13 @@
         <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>1.581530554767664</v>
+        <v>1.971677737898548</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6485487656071858</v>
+        <v>0.5070805655253631</v>
       </c>
       <c r="N24" t="n">
-        <v>15.94811007851097</v>
+        <v>25.35100588482284</v>
       </c>
     </row>
     <row r="25">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>UB01</t>
+          <t>UB02</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1761,27 +1761,27 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>B-BAT-01</t>
+          <t>B-BAT-04</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>S012</t>
+          <t>S013</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>S012-FOD-01</t>
+          <t>S013-FOD-01</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>58.33277518048336</v>
+        <v>81.81546099339445</v>
       </c>
       <c r="H25" t="n">
-        <v>77.51618711413991</v>
+        <v>97.50933665781729</v>
       </c>
       <c r="I25" t="n">
-        <v>88.36859904779647</v>
+        <v>104.952101211129</v>
       </c>
       <c r="J25" t="n">
         <v>120</v>
@@ -1790,13 +1790,13 @@
         <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>1.971677737898548</v>
+        <v>1.309771480726076</v>
       </c>
       <c r="M25" t="n">
-        <v>0.5070805655253631</v>
+        <v>0.672557129818481</v>
       </c>
       <c r="N25" t="n">
-        <v>25.35100588482284</v>
+        <v>20.57057180524388</v>
       </c>
     </row>
     <row r="26">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>UA04</t>
+          <t>UA01</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1815,27 +1815,27 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>A-BAT-03</t>
+          <t>A-BAT-05</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>S013</t>
+          <t>S014</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>S013-FOD-01</t>
+          <t>S014-FOD-01</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>88.6053446982134</v>
+        <v>71.85227137039857</v>
       </c>
       <c r="H26" t="n">
-        <v>105.6460815578028</v>
+        <v>92.06894339997392</v>
       </c>
       <c r="I26" t="n">
-        <v>114.4357073062812</v>
+        <v>104.0337265406604</v>
       </c>
       <c r="J26" t="n">
         <v>120</v>
@@ -1844,13 +1844,13 @@
         <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>1.575202255282084</v>
+        <v>1.905166317898852</v>
       </c>
       <c r="M26" t="n">
-        <v>0.6499550543817592</v>
+        <v>0.5766297071335885</v>
       </c>
       <c r="N26" t="n">
-        <v>15.91764048839522</v>
+        <v>17.50635634543891</v>
       </c>
     </row>
     <row r="27">
@@ -1859,52 +1859,52 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>UB02</t>
+          <t>UC02</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>B-BAT-03</t>
+          <t>C-BAT-03</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>S014</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>S014-FOD-01</t>
+          <t>S005-WAT-01,S005-WAT-02,S005-WAT-03,S005-MED-01</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>82.11655978878755</v>
+        <v>73.40239789956115</v>
       </c>
       <c r="H27" t="n">
-        <v>100.8302013682233</v>
+        <v>94.03834924059366</v>
       </c>
       <c r="I27" t="n">
-        <v>111.2919540587701</v>
+        <v>102.3864672482928</v>
       </c>
       <c r="J27" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="K27" t="b">
         <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>1.607789512414177</v>
+        <v>3.517681856451785</v>
       </c>
       <c r="M27" t="n">
-        <v>0.5980526218964557</v>
+        <v>0.5602897679435269</v>
       </c>
       <c r="N27" t="n">
-        <v>22.72292425632461</v>
+        <v>29.76731393537263</v>
       </c>
     </row>
     <row r="28">
@@ -1913,37 +1913,37 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>UC02</t>
+          <t>UA04</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>C-BAT-03</t>
+          <t>A-BAT-01</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S009</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>S005-WAT-01,S005-WAT-02,S005-WAT-03,S005-MED-01</t>
+          <t>S009-WAT-01,S009-MED-01</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>73.40239789956115</v>
+        <v>78.0102504536203</v>
       </c>
       <c r="H28" t="n">
-        <v>94.03834924059366</v>
+        <v>96.77508560873922</v>
       </c>
       <c r="I28" t="n">
-        <v>102.3864672482928</v>
+        <v>106.1535874305248</v>
       </c>
       <c r="J28" t="n">
         <v>180</v>
@@ -1952,13 +1952,13 @@
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>3.517681856451785</v>
+        <v>1.8710546231918</v>
       </c>
       <c r="M28" t="n">
-        <v>0.5602897679435269</v>
+        <v>0.5842100837351556</v>
       </c>
       <c r="N28" t="n">
-        <v>29.76731393537263</v>
+        <v>17.34211485240496</v>
       </c>
     </row>
     <row r="29">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>UA01</t>
+          <t>UA02</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1977,27 +1977,27 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>A-BAT-05</t>
+          <t>A-BAT-04</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>S009</t>
+          <t>S011</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>S009-WAT-01,S009-MED-01</t>
+          <t>S011-WAT-01,S011-MED-01</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>90.79957716162518</v>
+        <v>85.31830920904048</v>
       </c>
       <c r="H29" t="n">
-        <v>109.5644123167441</v>
+        <v>100.1509859376596</v>
       </c>
       <c r="I29" t="n">
-        <v>118.9429141385297</v>
+        <v>105.5774404440565</v>
       </c>
       <c r="J29" t="n">
         <v>180</v>
@@ -2006,13 +2006,13 @@
         <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>1.8710546231918</v>
+        <v>0.974739867166567</v>
       </c>
       <c r="M29" t="n">
-        <v>0.5842100837351556</v>
+        <v>0.7833911406296518</v>
       </c>
       <c r="N29" t="n">
-        <v>17.34211485240496</v>
+        <v>13.02652528635754</v>
       </c>
     </row>
     <row r="30">
@@ -2021,37 +2021,37 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>UA03</t>
+          <t>UB02</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>A-BAT-02</t>
+          <t>B-BAT-01</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>S011</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>S011-WAT-01,S011-MED-01</t>
+          <t>S001-HYG-01,S001-HYG-02</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>102.9244183821658</v>
+        <v>104.952101211129</v>
       </c>
       <c r="H30" t="n">
-        <v>117.757095110785</v>
+        <v>119.3249947674968</v>
       </c>
       <c r="I30" t="n">
-        <v>123.1835496171819</v>
+        <v>124.2604438794202</v>
       </c>
       <c r="J30" t="n">
         <v>180</v>
@@ -2060,13 +2060,13 @@
         <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>0.974739867166567</v>
+        <v>0.8736555559417358</v>
       </c>
       <c r="M30" t="n">
-        <v>0.7833911406296518</v>
+        <v>0.7815861110145661</v>
       </c>
       <c r="N30" t="n">
-        <v>13.02652528635754</v>
+        <v>17.42084568180142</v>
       </c>
     </row>
     <row r="31">
@@ -2075,37 +2075,37 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>UB01</t>
+          <t>UC01</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>B-BAT-04</t>
+          <t>C-BAT-02</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S003</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>S001-HYG-01,S001-HYG-02</t>
+          <t>S003-FOD-01,S003-FOD-02</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>88.36859904779647</v>
+        <v>86.05407488822445</v>
       </c>
       <c r="H31" t="n">
-        <v>102.7414926041643</v>
+        <v>109.0023288480263</v>
       </c>
       <c r="I31" t="n">
-        <v>107.6769417160876</v>
+        <v>122.1019161411614</v>
       </c>
       <c r="J31" t="n">
         <v>180</v>
@@ -2114,13 +2114,13 @@
         <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>0.8736555559417358</v>
+        <v>4.478907793936024</v>
       </c>
       <c r="M31" t="n">
-        <v>0.7815861110145661</v>
+        <v>0.440136525757997</v>
       </c>
       <c r="N31" t="n">
-        <v>17.42084568180142</v>
+        <v>34.10618101429455</v>
       </c>
     </row>
     <row r="32">
@@ -2129,37 +2129,37 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>UB01</t>
+          <t>UA03</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>B-BAT-02</t>
+          <t>A-BAT-02</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>S003-FOD-01,S003-FOD-02</t>
+          <t>S002-HYG-01</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>109.4103180975419</v>
+        <v>97.0571796331528</v>
       </c>
       <c r="H32" t="n">
-        <v>130.8178553859717</v>
+        <v>117.4755011442315</v>
       </c>
       <c r="I32" t="n">
-        <v>142.9596148966238</v>
+        <v>129.4958226553101</v>
       </c>
       <c r="J32" t="n">
         <v>180</v>
@@ -2168,13 +2168,13 @@
         <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>2.171939602406073</v>
+        <v>2.306810552860246</v>
       </c>
       <c r="M32" t="n">
-        <v>0.4570150993984818</v>
+        <v>0.4873754326977231</v>
       </c>
       <c r="N32" t="n">
-        <v>26.79734157293274</v>
+        <v>19.440198958216</v>
       </c>
     </row>
     <row r="33">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>UA02</t>
+          <t>UA01</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2193,27 +2193,27 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>A-BAT-04</t>
+          <t>A-BAT-03</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S004</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>S002-HYG-01</t>
+          <t>S004-FOD-01</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>102.9931829663858</v>
+        <v>104.0337265406604</v>
       </c>
       <c r="H33" t="n">
-        <v>123.4115044774644</v>
+        <v>126.0029030946436</v>
       </c>
       <c r="I33" t="n">
-        <v>135.4318259885431</v>
+        <v>139.5838574264045</v>
       </c>
       <c r="J33" t="n">
         <v>180</v>
@@ -2222,13 +2222,13 @@
         <v>1</v>
       </c>
       <c r="L33" t="n">
-        <v>2.306810552860246</v>
+        <v>2.494804901151978</v>
       </c>
       <c r="M33" t="n">
-        <v>0.4873754326977231</v>
+        <v>0.445598910855116</v>
       </c>
       <c r="N33" t="n">
-        <v>19.440198958216</v>
+        <v>20.34535693147248</v>
       </c>
     </row>
     <row r="34">
@@ -2237,37 +2237,37 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>UC01</t>
+          <t>UA02</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>C-BAT-02</t>
+          <t>A-BAT-06</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>S004</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>S004-FOD-01</t>
+          <t>S006-HYG-01</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>86.05407488822445</v>
+        <v>107.1800946266517</v>
       </c>
       <c r="H34" t="n">
-        <v>107.0726497510757</v>
+        <v>121.7413767262073</v>
       </c>
       <c r="I34" t="n">
-        <v>119.1588912805937</v>
+        <v>128.0105477146518</v>
       </c>
       <c r="J34" t="n">
         <v>180</v>
@@ -2276,13 +2276,13 @@
         <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>4.403269646749423</v>
+        <v>1.057798217128584</v>
       </c>
       <c r="M34" t="n">
-        <v>0.4495912941563222</v>
+        <v>0.7649337295269814</v>
       </c>
       <c r="N34" t="n">
-        <v>33.7647588221328</v>
+        <v>13.42643586024874</v>
       </c>
     </row>
     <row r="35">
@@ -2291,37 +2291,37 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>UA04</t>
+          <t>UB01</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>A-BAT-01</t>
+          <t>B-BAT-02</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S007</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>S006-HYG-01</t>
+          <t>S007-HYG-01</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>118.8725284606768</v>
+        <v>106.4826699159122</v>
       </c>
       <c r="H35" t="n">
-        <v>133.4338105602324</v>
+        <v>123.1528953251573</v>
       </c>
       <c r="I35" t="n">
-        <v>139.7029815486769</v>
+        <v>131.5684540677358</v>
       </c>
       <c r="J35" t="n">
         <v>180</v>
@@ -2330,13 +2330,13 @@
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>1.057798217128584</v>
+        <v>1.304041604369885</v>
       </c>
       <c r="M35" t="n">
-        <v>0.7649337295269814</v>
+        <v>0.6739895989075286</v>
       </c>
       <c r="N35" t="n">
-        <v>13.42643586024874</v>
+        <v>20.52918936489361</v>
       </c>
     </row>
     <row r="36">
@@ -2345,37 +2345,37 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>UC02</t>
+          <t>UB02</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>C-BAT-04</t>
+          <t>B-BAT-04</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>S007</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>S007-HYG-01</t>
+          <t>S008-FOD-01</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>111.8491029475612</v>
+        <v>125.5226730163729</v>
       </c>
       <c r="H36" t="n">
-        <v>129.797838769108</v>
+        <v>145.0327011399565</v>
       </c>
       <c r="I36" t="n">
-        <v>139.0145745906547</v>
+        <v>156.2018403746513</v>
       </c>
       <c r="J36" t="n">
         <v>180</v>
@@ -2384,13 +2384,13 @@
         <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>2.845453629675534</v>
+        <v>2.113150583946663</v>
       </c>
       <c r="M36" t="n">
-        <v>0.6443182962905583</v>
+        <v>0.4717123540133343</v>
       </c>
       <c r="N36" t="n">
-        <v>26.73295041172984</v>
+        <v>26.37275421739256</v>
       </c>
     </row>
     <row r="37">
@@ -2399,37 +2399,37 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>UB02</t>
+          <t>UA04</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>B-BAT-01</t>
+          <t>A-BAT-04</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S015</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>S008-FOD-01</t>
+          <t>S015-WAT-01</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>113.7196049326193</v>
+        <v>118.6039657304141</v>
       </c>
       <c r="H37" t="n">
-        <v>133.229633056203</v>
+        <v>138.5433077102512</v>
       </c>
       <c r="I37" t="n">
-        <v>144.3987722908978</v>
+        <v>150.3679830234216</v>
       </c>
       <c r="J37" t="n">
         <v>180</v>
@@ -2438,13 +2438,13 @@
         <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>2.113150583946663</v>
+        <v>2.064880504882156</v>
       </c>
       <c r="M37" t="n">
-        <v>0.4717123540133343</v>
+        <v>0.5411376655817433</v>
       </c>
       <c r="N37" t="n">
-        <v>26.37275421739256</v>
+        <v>18.27535057906223</v>
       </c>
     </row>
     <row r="38">
@@ -2453,52 +2453,52 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>UC01</t>
+          <t>UA02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>C-BAT-01</t>
+          <t>A-BAT-05</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>S015</t>
+          <t>S003</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>S015-WAT-01</t>
+          <t>S003-HYG-01</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>121.9728032321447</v>
+        <v>128.0105477146518</v>
       </c>
       <c r="H38" t="n">
-        <v>141.4875062070714</v>
+        <v>150.4350476533466</v>
       </c>
       <c r="I38" t="n">
-        <v>152.480209181998</v>
+        <v>164.5937698142636</v>
       </c>
       <c r="J38" t="n">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="K38" t="b">
         <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>3.686771208193226</v>
+        <v>2.412427120788479</v>
       </c>
       <c r="M38" t="n">
-        <v>0.5391535989758467</v>
+        <v>0.4639050842692268</v>
       </c>
       <c r="N38" t="n">
-        <v>30.53056448142775</v>
+        <v>19.94872317416675</v>
       </c>
     </row>
     <row r="39">
@@ -2507,7 +2507,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>UA01</t>
+          <t>UA03</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2517,27 +2517,27 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>A-BAT-06</t>
+          <t>A-BAT-01</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S004</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>S003-HYG-01</t>
+          <t>S004-HYG-01</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>118.9429141385297</v>
+        <v>129.4958226553101</v>
       </c>
       <c r="H39" t="n">
-        <v>141.3674140772245</v>
+        <v>151.4649992092933</v>
       </c>
       <c r="I39" t="n">
-        <v>155.5261362381415</v>
+        <v>165.0459535410543</v>
       </c>
       <c r="J39" t="n">
         <v>240</v>
@@ -2546,13 +2546,13 @@
         <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>2.412427120788479</v>
+        <v>2.474777359477118</v>
       </c>
       <c r="M39" t="n">
-        <v>0.4639050842692268</v>
+        <v>0.4500494756717516</v>
       </c>
       <c r="N39" t="n">
-        <v>19.94872317416675</v>
+        <v>20.24892802711205</v>
       </c>
     </row>
     <row r="40">
@@ -2561,37 +2561,37 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>UC02</t>
+          <t>UB01</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>C-BAT-03</t>
+          <t>B-BAT-03</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>S004</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>S004-HYG-01</t>
+          <t>S005-FOD-01</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>139.0145745906547</v>
+        <v>131.833675800735</v>
       </c>
       <c r="H40" t="n">
-        <v>160.033149453506</v>
+        <v>148.143708746864</v>
       </c>
       <c r="I40" t="n">
-        <v>172.119390983024</v>
+        <v>156.0285194707708</v>
       </c>
       <c r="J40" t="n">
         <v>240</v>
@@ -2600,13 +2600,13 @@
         <v>1</v>
       </c>
       <c r="L40" t="n">
-        <v>4.375001305345046</v>
+        <v>1.42178203198294</v>
       </c>
       <c r="M40" t="n">
-        <v>0.4531248368318692</v>
+        <v>0.6445544920042652</v>
       </c>
       <c r="N40" t="n">
-        <v>33.63715866996027</v>
+        <v>21.37953689765456</v>
       </c>
     </row>
     <row r="41">
@@ -2615,37 +2615,37 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>UA03</t>
+          <t>UC02</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>A-BAT-03</t>
+          <t>C-BAT-04</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>S005-FOD-01</t>
+          <t>S008-HYG-01</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>130.3533477946764</v>
+        <v>111.8491029475612</v>
       </c>
       <c r="H41" t="n">
-        <v>148.1361620762771</v>
+        <v>132.391869285176</v>
       </c>
       <c r="I41" t="n">
-        <v>157.4937541356557</v>
+        <v>144.0733022894574</v>
       </c>
       <c r="J41" t="n">
         <v>240</v>
@@ -2654,13 +2654,13 @@
         <v>1</v>
       </c>
       <c r="L41" t="n">
-        <v>1.711944804864733</v>
+        <v>4.438133580673728</v>
       </c>
       <c r="M41" t="n">
-        <v>0.6195678211411705</v>
+        <v>0.445233302415784</v>
       </c>
       <c r="N41" t="n">
-        <v>16.57603054194131</v>
+        <v>33.92213074609668</v>
       </c>
     </row>
     <row r="42">
@@ -2669,37 +2669,37 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>UB01</t>
+          <t>UA01</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>B-BAT-04</t>
+          <t>A-BAT-06</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S009</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>S008-HYG-01</t>
+          <t>S009-FOD-01</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>142.9596148966238</v>
+        <v>141.4369835749006</v>
       </c>
       <c r="H42" t="n">
-        <v>162.4696430202075</v>
+        <v>159.2018187300195</v>
       </c>
       <c r="I42" t="n">
-        <v>173.6387822549022</v>
+        <v>168.580320551805</v>
       </c>
       <c r="J42" t="n">
         <v>240</v>
@@ -2708,13 +2708,13 @@
         <v>1</v>
       </c>
       <c r="L42" t="n">
-        <v>2.080451140464154</v>
+        <v>1.797687027182534</v>
       </c>
       <c r="M42" t="n">
-        <v>0.4798872148839615</v>
+        <v>0.6005139939594369</v>
       </c>
       <c r="N42" t="n">
-        <v>26.13659157001889</v>
+        <v>16.9888634642122</v>
       </c>
     </row>
     <row r="43">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>UA02</t>
+          <t>UA04</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2738,22 +2738,22 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>S009</t>
+          <t>S011</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>S009-FOD-01</t>
+          <t>S011-FOD-01</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>136.2100749035394</v>
+        <v>150.3679830234216</v>
       </c>
       <c r="H43" t="n">
-        <v>153.9749100586583</v>
+        <v>164.2006597520408</v>
       </c>
       <c r="I43" t="n">
-        <v>163.3534118804439</v>
+        <v>169.6271142584377</v>
       </c>
       <c r="J43" t="n">
         <v>240</v>
@@ -2762,13 +2762,13 @@
         <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>1.797687027182534</v>
+        <v>0.9386225872442431</v>
       </c>
       <c r="M43" t="n">
-        <v>0.6005139939594369</v>
+        <v>0.7914172028346127</v>
       </c>
       <c r="N43" t="n">
-        <v>16.9888634642122</v>
+        <v>12.85262727191672</v>
       </c>
     </row>
     <row r="44">
@@ -2787,27 +2787,27 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>C-BAT-02</t>
+          <t>C-BAT-01</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>S011</t>
+          <t>S015</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>S011-FOD-01</t>
+          <t>S015-FOD-01</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>152.9236501027265</v>
+        <v>122.1019161411614</v>
       </c>
       <c r="H44" t="n">
-        <v>166.8837186611424</v>
+        <v>141.616619116088</v>
       </c>
       <c r="I44" t="n">
-        <v>171.884453886225</v>
+        <v>152.6093220910147</v>
       </c>
       <c r="J44" t="n">
         <v>240</v>
@@ -2816,13 +2816,13 @@
         <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>1.681614284379605</v>
+        <v>3.616951951699551</v>
       </c>
       <c r="M44" t="n">
-        <v>0.7897982144525494</v>
+        <v>0.5478810060375561</v>
       </c>
       <c r="N44" t="n">
-        <v>21.47950892254682</v>
+        <v>30.21540811531047</v>
       </c>
     </row>
     <row r="45">
@@ -2831,106 +2831,52 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>UB02</t>
+          <t>UC02</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>B-BAT-03</t>
+          <t>C-BAT-03</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>S015</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>S015-FOD-01</t>
+          <t>S005-HYG-01</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>144.3987722908978</v>
+        <v>144.0733022894574</v>
       </c>
       <c r="H45" t="n">
-        <v>162.6661404833473</v>
+        <v>161.4092536304899</v>
       </c>
       <c r="I45" t="n">
-        <v>172.8188420091302</v>
+        <v>169.7573716381891</v>
       </c>
       <c r="J45" t="n">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="K45" t="b">
         <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>1.684852321935074</v>
+        <v>3.005558200720436</v>
       </c>
       <c r="M45" t="n">
-        <v>0.5787869195162316</v>
+        <v>0.6243052249099456</v>
       </c>
       <c r="N45" t="n">
-        <v>23.2794889917533</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>UA04</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>A-BAT-05</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>S005</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>S005-HYG-01</t>
-        </is>
-      </c>
-      <c r="G46" t="n">
-        <v>139.7029815486769</v>
-      </c>
-      <c r="H46" t="n">
-        <v>157.4857958302777</v>
-      </c>
-      <c r="I46" t="n">
-        <v>166.8433878896562</v>
-      </c>
-      <c r="J46" t="n">
-        <v>300</v>
-      </c>
-      <c r="K46" t="b">
-        <v>1</v>
-      </c>
-      <c r="L46" t="n">
-        <v>1.698235657333516</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0.6226142983703299</v>
-      </c>
-      <c r="N46" t="n">
-        <v>16.51002353530952</v>
+        <v>27.45564465602974</v>
       </c>
     </row>
   </sheetData>
@@ -3515,16 +3461,16 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>UA01</t>
+          <t>UB01</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>15.56128209955562</v>
+        <v>14.67766295665795</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -3536,7 +3482,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S006-MED-01</t>
+          <t>S006-WAT-02</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -3549,16 +3495,16 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>UA01</t>
+          <t>UB01</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>15.56128209955562</v>
+        <v>14.67766295665795</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -3570,7 +3516,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S007-WAT-01</t>
+          <t>S006-WAT-03</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -3578,12 +3524,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>S007</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>UB01</t>
+          <t>UB02</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3592,7 +3538,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>17.67022540924516</v>
+        <v>14.67766295665795</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -3604,7 +3550,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S007-WAT-02</t>
+          <t>S006-MED-01</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -3612,12 +3558,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>S007</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>UB01</t>
+          <t>UB02</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -3626,7 +3572,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>17.67022540924516</v>
+        <v>14.67766295665795</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -3638,7 +3584,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S010-WAT-01</t>
+          <t>S007-WAT-01</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -3646,21 +3592,21 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>S010</t>
+          <t>S007</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>UB02</t>
+          <t>UA01</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>17.01750341526321</v>
+        <v>18.92962030802469</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -3672,7 +3618,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S010-MED-01</t>
+          <t>S007-MED-01</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -3680,21 +3626,21 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>S010</t>
+          <t>S007</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>UB02</t>
+          <t>UA01</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>17.01750341526321</v>
+        <v>18.92962030802469</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
@@ -3706,7 +3652,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S013-WAT-01</t>
+          <t>S010-WAT-01</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -3714,7 +3660,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>S013</t>
+          <t>S010</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3728,7 +3674,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>18.04073685958943</v>
+        <v>18.34484599897648</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -3740,7 +3686,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S013-MED-01</t>
+          <t>S010-MED-01</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -3748,7 +3694,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>S013</t>
+          <t>S010</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3762,7 +3708,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>18.04073685958943</v>
+        <v>18.34484599897648</v>
       </c>
       <c r="G24" t="n">
         <v>60</v>
@@ -3774,7 +3720,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S012-WAT-01</t>
+          <t>S013-WAT-01</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -3782,21 +3728,21 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>S012</t>
+          <t>S013</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>UA03</t>
+          <t>UB01</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>22.2385339731365</v>
+        <v>36.75709046662761</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -3808,7 +3754,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S012-MED-01</t>
+          <t>S013-MED-01</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -3816,21 +3762,21 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>S012</t>
+          <t>S013</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>UA03</t>
+          <t>UB01</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>22.2385339731365</v>
+        <v>36.75709046662761</v>
       </c>
       <c r="G26" t="n">
         <v>60</v>
@@ -3842,7 +3788,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S014-WAT-01</t>
+          <t>S012-WAT-01</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -3850,12 +3796,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>S014</t>
+          <t>S012</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>UA04</t>
+          <t>UA03</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3864,7 +3810,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>21.21667202957535</v>
+        <v>22.2385339731365</v>
       </c>
       <c r="G27" t="n">
         <v>60</v>
@@ -3876,7 +3822,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S014-MED-01</t>
+          <t>S012-MED-01</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -3884,12 +3830,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>S014</t>
+          <t>S012</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>UA04</t>
+          <t>UA03</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3898,7 +3844,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>21.21667202957535</v>
+        <v>22.2385339731365</v>
       </c>
       <c r="G28" t="n">
         <v>60</v>
@@ -3910,7 +3856,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S006-WAT-02</t>
+          <t>S014-WAT-01</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -3918,12 +3864,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S014</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>UA01</t>
+          <t>UA04</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3932,7 +3878,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>36.39173518755575</v>
+        <v>21.21667202957535</v>
       </c>
       <c r="G29" t="n">
         <v>60</v>
@@ -3944,20 +3890,20 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S006-WAT-03</t>
+          <t>S014-MED-01</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S014</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>UA02</t>
+          <t>UA04</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3966,7 +3912,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>41.39164470762339</v>
+        <v>21.21667202957535</v>
       </c>
       <c r="G30" t="n">
         <v>60</v>
@@ -3978,11 +3924,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S007-MED-01</t>
+          <t>S007-WAT-02</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3991,16 +3937,16 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>UB02</t>
+          <t>UA02</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>41.45401001754935</v>
+        <v>45.36809008375543</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -4016,7 +3962,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4050,7 +3996,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4084,7 +4030,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4118,7 +4064,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4152,7 +4098,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4186,7 +4132,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4220,7 +4166,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4254,7 +4200,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4288,7 +4234,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4297,7 +4243,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>UB01</t>
+          <t>UB02</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4306,7 +4252,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>46.90339077726461</v>
+        <v>40.88082142764576</v>
       </c>
       <c r="G40" t="n">
         <v>120</v>
@@ -4322,7 +4268,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4331,7 +4277,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>UB01</t>
+          <t>UB02</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4340,7 +4286,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>46.90339077726461</v>
+        <v>40.88082142764576</v>
       </c>
       <c r="G41" t="n">
         <v>120</v>
@@ -4356,7 +4302,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4365,7 +4311,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>UB02</t>
+          <t>UB01</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4374,7 +4320,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>70.68717538556881</v>
+        <v>65.01746164538029</v>
       </c>
       <c r="G42" t="n">
         <v>120</v>
@@ -4390,7 +4336,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4399,7 +4345,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>UB02</t>
+          <t>UB01</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4408,7 +4354,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>70.68717538556881</v>
+        <v>65.01746164538029</v>
       </c>
       <c r="G43" t="n">
         <v>120</v>
@@ -4424,7 +4370,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4433,7 +4379,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>UA04</t>
+          <t>UA01</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4442,7 +4388,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>50.71669070780122</v>
+        <v>43.82841392100908</v>
       </c>
       <c r="G44" t="n">
         <v>120</v>
@@ -4458,7 +4404,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -4467,7 +4413,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>UA04</t>
+          <t>UA01</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4476,7 +4422,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>50.71669070780122</v>
+        <v>43.82841392100908</v>
       </c>
       <c r="G45" t="n">
         <v>120</v>
@@ -4492,7 +4438,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -4501,7 +4447,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>UA03</t>
+          <t>UA04</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4510,7 +4456,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>64.46562709535644</v>
+        <v>65.09986638392333</v>
       </c>
       <c r="G46" t="n">
         <v>120</v>
@@ -4526,7 +4472,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -4535,7 +4481,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>UA03</t>
+          <t>UA04</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4544,7 +4490,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>64.46562709535644</v>
+        <v>65.09986638392333</v>
       </c>
       <c r="G47" t="n">
         <v>120</v>
@@ -4560,7 +4506,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -4569,16 +4515,16 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>UA01</t>
+          <t>UB02</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>70.96116026223557</v>
+        <v>70.57757402331404</v>
       </c>
       <c r="G48" t="n">
         <v>120</v>
@@ -4594,7 +4540,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -4603,7 +4549,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>UA02</t>
+          <t>UA03</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4612,7 +4558,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>69.60221348982112</v>
+        <v>59.00711924522805</v>
       </c>
       <c r="G49" t="n">
         <v>120</v>
@@ -4628,7 +4574,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -4637,7 +4583,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>UA04</t>
+          <t>UA01</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4646,7 +4592,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>71.06436833453876</v>
+        <v>65.58310038195407</v>
       </c>
       <c r="G50" t="n">
         <v>120</v>
@@ -4662,7 +4608,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -4680,7 +4626,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>93.31822932502776</v>
+        <v>73.30799382621946</v>
       </c>
       <c r="G51" t="n">
         <v>120</v>
@@ -4696,7 +4642,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -4714,7 +4660,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>93.83079460541157</v>
+        <v>82.13836077138644</v>
       </c>
       <c r="G52" t="n">
         <v>120</v>
@@ -4730,7 +4676,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -4748,7 +4694,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>77.51618711413991</v>
+        <v>95.6302579822556</v>
       </c>
       <c r="G53" t="n">
         <v>120</v>
@@ -4764,7 +4710,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -4773,16 +4719,16 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>UA04</t>
+          <t>UB02</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>105.6460815578028</v>
+        <v>97.50933665781729</v>
       </c>
       <c r="G54" t="n">
         <v>120</v>
@@ -4798,7 +4744,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -4807,16 +4753,16 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>UB02</t>
+          <t>UA01</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>100.8302013682233</v>
+        <v>92.06894339997392</v>
       </c>
       <c r="G55" t="n">
         <v>120</v>
@@ -4832,7 +4778,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -4866,7 +4812,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -4900,7 +4846,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -4934,7 +4880,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -4968,7 +4914,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -4977,7 +4923,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>UA01</t>
+          <t>UA04</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4986,7 +4932,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>109.5644123167441</v>
+        <v>96.77508560873922</v>
       </c>
       <c r="G60" t="n">
         <v>180</v>
@@ -5002,7 +4948,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -5011,7 +4957,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>UA01</t>
+          <t>UA04</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5020,7 +4966,7 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>109.5644123167441</v>
+        <v>96.77508560873922</v>
       </c>
       <c r="G61" t="n">
         <v>180</v>
@@ -5036,7 +4982,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -5045,7 +4991,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>UA03</t>
+          <t>UA02</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5054,7 +5000,7 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>117.757095110785</v>
+        <v>100.1509859376596</v>
       </c>
       <c r="G62" t="n">
         <v>180</v>
@@ -5070,7 +5016,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -5079,7 +5025,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>UA03</t>
+          <t>UA02</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5088,7 +5034,7 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>117.757095110785</v>
+        <v>100.1509859376596</v>
       </c>
       <c r="G63" t="n">
         <v>180</v>
@@ -5104,7 +5050,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -5113,7 +5059,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>UB01</t>
+          <t>UB02</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5122,7 +5068,7 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>102.7414926041643</v>
+        <v>119.3249947674968</v>
       </c>
       <c r="G64" t="n">
         <v>180</v>
@@ -5138,7 +5084,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -5147,7 +5093,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>UB01</t>
+          <t>UB02</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5156,7 +5102,7 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>102.7414926041643</v>
+        <v>119.3249947674968</v>
       </c>
       <c r="G65" t="n">
         <v>180</v>
@@ -5172,7 +5118,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -5181,16 +5127,16 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>UB01</t>
+          <t>UC01</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>130.8178553859717</v>
+        <v>109.0023288480263</v>
       </c>
       <c r="G66" t="n">
         <v>180</v>
@@ -5206,7 +5152,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -5215,16 +5161,16 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>UB01</t>
+          <t>UC01</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>130.8178553859717</v>
+        <v>109.0023288480263</v>
       </c>
       <c r="G67" t="n">
         <v>180</v>
@@ -5240,7 +5186,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -5249,7 +5195,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>UA02</t>
+          <t>UA03</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -5258,7 +5204,7 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>123.4115044774644</v>
+        <v>117.4755011442315</v>
       </c>
       <c r="G68" t="n">
         <v>180</v>
@@ -5274,7 +5220,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -5283,16 +5229,16 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>UC01</t>
+          <t>UA01</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>107.0726497510757</v>
+        <v>126.0029030946436</v>
       </c>
       <c r="G69" t="n">
         <v>180</v>
@@ -5308,7 +5254,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -5317,7 +5263,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>UA04</t>
+          <t>UA02</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -5326,7 +5272,7 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>133.4338105602324</v>
+        <v>121.7413767262073</v>
       </c>
       <c r="G70" t="n">
         <v>180</v>
@@ -5342,7 +5288,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -5351,16 +5297,16 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>UC02</t>
+          <t>UB01</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>129.797838769108</v>
+        <v>123.1528953251573</v>
       </c>
       <c r="G71" t="n">
         <v>180</v>
@@ -5376,7 +5322,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -5394,7 +5340,7 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>133.229633056203</v>
+        <v>145.0327011399565</v>
       </c>
       <c r="G72" t="n">
         <v>180</v>
@@ -5410,7 +5356,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -5419,16 +5365,16 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>UC01</t>
+          <t>UA04</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>141.4875062070714</v>
+        <v>138.5433077102512</v>
       </c>
       <c r="G73" t="n">
         <v>180</v>
@@ -5444,7 +5390,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -5453,7 +5399,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>UA01</t>
+          <t>UA02</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -5462,7 +5408,7 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>141.3674140772245</v>
+        <v>150.4350476533466</v>
       </c>
       <c r="G74" t="n">
         <v>240</v>
@@ -5478,7 +5424,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -5487,16 +5433,16 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>UC02</t>
+          <t>UA03</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>160.033149453506</v>
+        <v>151.4649992092933</v>
       </c>
       <c r="G75" t="n">
         <v>240</v>
@@ -5512,7 +5458,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -5521,16 +5467,16 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>UA03</t>
+          <t>UB01</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>148.1361620762771</v>
+        <v>148.143708746864</v>
       </c>
       <c r="G76" t="n">
         <v>240</v>
@@ -5546,7 +5492,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -5555,16 +5501,16 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>UB01</t>
+          <t>UC02</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>162.4696430202075</v>
+        <v>132.391869285176</v>
       </c>
       <c r="G77" t="n">
         <v>240</v>
@@ -5580,7 +5526,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -5589,7 +5535,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>UA02</t>
+          <t>UA01</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5598,7 +5544,7 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>153.9749100586583</v>
+        <v>159.2018187300195</v>
       </c>
       <c r="G78" t="n">
         <v>240</v>
@@ -5614,7 +5560,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -5623,16 +5569,16 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>UC01</t>
+          <t>UA04</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>166.8837186611424</v>
+        <v>164.2006597520408</v>
       </c>
       <c r="G79" t="n">
         <v>240</v>
@@ -5648,7 +5594,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -5657,16 +5603,16 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>UB02</t>
+          <t>UC01</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>162.6661404833473</v>
+        <v>141.616619116088</v>
       </c>
       <c r="G80" t="n">
         <v>240</v>
@@ -5682,7 +5628,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -5691,16 +5637,16 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>UA04</t>
+          <t>UC02</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>157.4857958302777</v>
+        <v>161.4092536304899</v>
       </c>
       <c r="G81" t="n">
         <v>300</v>
@@ -5894,7 +5840,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3">
@@ -5924,7 +5870,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>173.6387822549022</v>
+        <v>169.7573716381891</v>
       </c>
     </row>
     <row r="6">
@@ -5954,7 +5900,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>97.65260763126345</v>
+        <v>96.34603111683055</v>
       </c>
     </row>
     <row r="9">
@@ -5965,7 +5911,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EDD + bounded beam(80) + 1-swap LNS</t>
+          <t>EDD + bounded beam(320) + 1-swap LNS</t>
         </is>
       </c>
     </row>
